--- a/output/yearly_benthic_cover_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_25_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.15987586558737</v>
+        <v>44.90800215786603</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6064728467344</v>
+        <v>101.4339754146248</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93674718286491</v>
+        <v>88.05073790880499</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82432288337267</v>
+        <v>45.93393658262108</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22857730758662</v>
+        <v>2.228786718756852</v>
       </c>
       <c r="E3" t="n">
-        <v>5.642036253552237</v>
+        <v>5.710647605850639</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428591025288735</v>
+        <v>0.7429289062522839</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9377965502517</v>
+        <v>33.97469835062579</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17151871632818</v>
+        <v>34.17472968760506</v>
       </c>
       <c r="I3" t="n">
-        <v>6.57108986181184</v>
+        <v>6.575640975637596</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642869390805459</v>
+        <v>4.643305664076775</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0632528171351</v>
+        <v>11.949262091195</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87653964466989</v>
+        <v>48.88077547695217</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641153451777</v>
+        <v>106.7639741507683</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02685130199886</v>
+        <v>87.2111975179071</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5540247027495</v>
+        <v>42.73080465942621</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184657848069859</v>
+        <v>2.188728215682761</v>
       </c>
       <c r="E4" t="n">
-        <v>6.445415990324497</v>
+        <v>6.523209086363865</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444204513180364</v>
+        <v>0.7444881756188095</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26897089336165</v>
+        <v>33.36406317998955</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24334076062967</v>
+        <v>34.24645607846524</v>
       </c>
       <c r="I4" t="n">
-        <v>5.487417537557437</v>
+        <v>5.491201684169305</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652627820737727</v>
+        <v>4.65305109761756</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97314869800112</v>
+        <v>12.7888024820929</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29029632531017</v>
+        <v>44.29773616471316</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81746972606081</v>
+        <v>99.81734330623229</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94487186080993</v>
+        <v>86.17872673432306</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32362706654583</v>
+        <v>42.55068477464999</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132023633117568</v>
+        <v>2.138806302127441</v>
       </c>
       <c r="E5" t="n">
-        <v>7.05362421404424</v>
+        <v>7.138442748028337</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745743070339228</v>
+        <v>0.7458082305166921</v>
       </c>
       <c r="G5" t="n">
-        <v>32.4674329469094</v>
+        <v>32.60307427968147</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30418123560449</v>
+        <v>34.30717860376784</v>
       </c>
       <c r="I5" t="n">
-        <v>4.580972571174825</v>
+        <v>4.584115129471955</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660894189620175</v>
+        <v>4.661301440729326</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05512813919008</v>
+        <v>13.82127326567696</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46881652933193</v>
+        <v>43.47550857955721</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84757173506785</v>
+        <v>99.84746661988416</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.66015144994267</v>
+        <v>84.87648468677946</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75034964398414</v>
+        <v>41.96057216968146</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069375283101132</v>
+        <v>2.075415134803628</v>
       </c>
       <c r="E6" t="n">
-        <v>7.483561264811027</v>
+        <v>7.564508769111014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468656537952223</v>
+        <v>0.7469288156223994</v>
       </c>
       <c r="G6" t="n">
-        <v>31.51339516243189</v>
+        <v>31.63676567339101</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35582007458022</v>
+        <v>34.35872551863037</v>
       </c>
       <c r="I6" t="n">
-        <v>3.823223675003033</v>
+        <v>3.825835677581034</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667910336220139</v>
+        <v>4.668305097639997</v>
       </c>
       <c r="K6" t="n">
-        <v>15.33984855005732</v>
+        <v>15.12351531322054</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78255256787035</v>
+        <v>42.78857598572379</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87275076191182</v>
+        <v>99.87266346862579</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.2126099741172</v>
+        <v>83.46247062248813</v>
       </c>
       <c r="C7" t="n">
-        <v>40.89665917650868</v>
+        <v>41.14097039496741</v>
       </c>
       <c r="D7" t="n">
-        <v>1.998983374572741</v>
+        <v>2.006873075770615</v>
       </c>
       <c r="E7" t="n">
-        <v>7.760682154918915</v>
+        <v>7.846729014009187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478200642222084</v>
+        <v>0.7478810966498984</v>
       </c>
       <c r="G7" t="n">
-        <v>30.44143492022359</v>
+        <v>30.59193901484188</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39972295422158</v>
+        <v>34.40253044589533</v>
       </c>
       <c r="I7" t="n">
-        <v>3.190091104569376</v>
+        <v>3.192261121259346</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673875401388802</v>
+        <v>4.674256854061865</v>
       </c>
       <c r="K7" t="n">
-        <v>16.78739002588279</v>
+        <v>16.53752937751188</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20975013996956</v>
+        <v>42.21522701425456</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89379934236102</v>
+        <v>99.89372678673385</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.07082486470395</v>
+        <v>88.28355762169917</v>
       </c>
       <c r="C8" t="n">
-        <v>43.21908384787483</v>
+        <v>43.42873516199653</v>
       </c>
       <c r="D8" t="n">
-        <v>2.00322296392361</v>
+        <v>2.011119041048955</v>
       </c>
       <c r="E8" t="n">
-        <v>9.605105301512557</v>
+        <v>9.667996216005543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494060954123481</v>
+        <v>0.7494633975970988</v>
       </c>
       <c r="G8" t="n">
-        <v>30.95301166389408</v>
+        <v>31.09203919978141</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47268038896801</v>
+        <v>34.47531628946655</v>
       </c>
       <c r="I8" t="n">
-        <v>5.60361035466617</v>
+        <v>5.603477242817765</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683788096327175</v>
+        <v>4.684146234981868</v>
       </c>
       <c r="K8" t="n">
-        <v>11.92917513529605</v>
+        <v>11.7164423783008</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66534931808012</v>
+        <v>44.66843422874314</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81360830125101</v>
+        <v>99.81361176904048</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.12502329354857</v>
+        <v>86.3102903205577</v>
       </c>
       <c r="C9" t="n">
-        <v>42.14322366951306</v>
+        <v>42.32561128146065</v>
       </c>
       <c r="D9" t="n">
-        <v>1.915101662404923</v>
+        <v>1.921800898919705</v>
       </c>
       <c r="E9" t="n">
-        <v>9.962267370438376</v>
+        <v>10.01828639473393</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750762967530046</v>
+        <v>0.7508174232001448</v>
       </c>
       <c r="G9" t="n">
-        <v>29.59139604602846</v>
+        <v>29.71117455693767</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53509650638211</v>
+        <v>34.53760146720666</v>
       </c>
       <c r="I9" t="n">
-        <v>4.67813019370186</v>
+        <v>4.678000684558683</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692268547062787</v>
+        <v>4.692608895000905</v>
       </c>
       <c r="K9" t="n">
-        <v>13.87497670645144</v>
+        <v>13.68970967944229</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82614378085033</v>
+        <v>43.82902689346322</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84434415681483</v>
+        <v>99.84434785436616</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.04719466539443</v>
+        <v>84.11011121805556</v>
       </c>
       <c r="C10" t="n">
-        <v>40.79143972292849</v>
+        <v>40.85162248858913</v>
       </c>
       <c r="D10" t="n">
-        <v>1.821960815961155</v>
+        <v>1.823100586058678</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12849958084676</v>
+        <v>10.15449247988671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519255437083738</v>
+        <v>0.7519791804457482</v>
       </c>
       <c r="G10" t="n">
-        <v>28.15222039844495</v>
+        <v>28.18526090694054</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58857501058519</v>
+        <v>34.59104230050442</v>
       </c>
       <c r="I10" t="n">
-        <v>3.90447866767067</v>
+        <v>3.904365886433531</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699534648177336</v>
+        <v>4.699869877785926</v>
       </c>
       <c r="K10" t="n">
-        <v>15.95280533460556</v>
+        <v>15.88988878194443</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12580688152978</v>
+        <v>43.12854426600647</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87005193906384</v>
+        <v>99.87005553654004</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.81568303118959</v>
+        <v>81.8445580371171</v>
       </c>
       <c r="C11" t="n">
-        <v>39.16538340859954</v>
+        <v>39.19155301217567</v>
       </c>
       <c r="D11" t="n">
-        <v>1.722861785024118</v>
+        <v>1.722543591335215</v>
       </c>
       <c r="E11" t="n">
-        <v>10.12060466913748</v>
+        <v>10.1373924004183</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529236457171862</v>
+        <v>0.7529769721655033</v>
       </c>
       <c r="G11" t="n">
-        <v>26.62098123250272</v>
+        <v>26.6306428271856</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63448770299055</v>
+        <v>34.63694071961316</v>
       </c>
       <c r="I11" t="n">
-        <v>3.258051210085129</v>
+        <v>3.257955450364916</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705772785732413</v>
+        <v>4.706106076034396</v>
       </c>
       <c r="K11" t="n">
-        <v>18.18431696881041</v>
+        <v>18.15544196288288</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54184188182141</v>
+        <v>42.54455041698496</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89154225923136</v>
+        <v>99.89154539204353</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.47706505291681</v>
+        <v>79.57434487996272</v>
       </c>
       <c r="C12" t="n">
-        <v>37.33126046662056</v>
+        <v>37.42583644650092</v>
       </c>
       <c r="D12" t="n">
-        <v>1.619957367636383</v>
+        <v>1.622791810983053</v>
       </c>
       <c r="E12" t="n">
-        <v>9.969136363164612</v>
+        <v>10.00334925126008</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537819856913195</v>
+        <v>0.7538342971127501</v>
       </c>
       <c r="G12" t="n">
-        <v>25.03094273502559</v>
+        <v>25.08847341719397</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67397134180069</v>
+        <v>34.67637766718651</v>
       </c>
       <c r="I12" t="n">
-        <v>2.718137849027487</v>
+        <v>2.718054079271667</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711137410570746</v>
+        <v>4.711464356954688</v>
       </c>
       <c r="K12" t="n">
-        <v>20.52293494708319</v>
+        <v>20.42565512003727</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05530316379391</v>
+        <v>42.05800967095165</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90949857749764</v>
+        <v>99.90950123748985</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.97336133116553</v>
+        <v>77.2601312112333</v>
       </c>
       <c r="C13" t="n">
-        <v>35.24763387546488</v>
+        <v>35.53174261883036</v>
       </c>
       <c r="D13" t="n">
-        <v>1.510683085862043</v>
+        <v>1.521990544350319</v>
       </c>
       <c r="E13" t="n">
-        <v>9.67455773674549</v>
+        <v>9.75985842397511</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545221028819016</v>
+        <v>0.7545716929136753</v>
       </c>
       <c r="G13" t="n">
-        <v>23.34247960374242</v>
+        <v>23.5300788768599</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70801673256747</v>
+        <v>34.71029787402907</v>
       </c>
       <c r="I13" t="n">
-        <v>2.267338926354328</v>
+        <v>2.267260718394747</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715763143011884</v>
+        <v>4.716073080710471</v>
       </c>
       <c r="K13" t="n">
-        <v>23.02663866883447</v>
+        <v>22.73986878876671</v>
       </c>
       <c r="L13" t="n">
-        <v>41.650223626561</v>
+        <v>41.65288709020092</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92449617086035</v>
+        <v>99.924498497798</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.72428221720806</v>
+        <v>84.01132561097575</v>
       </c>
       <c r="C14" t="n">
-        <v>39.29989155876881</v>
+        <v>39.67356817442688</v>
       </c>
       <c r="D14" t="n">
-        <v>1.512579584372194</v>
+        <v>1.523809355874481</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96081632235049</v>
+        <v>12.07849836602747</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554693234190106</v>
+        <v>0.7554734223600061</v>
       </c>
       <c r="G14" t="n">
-        <v>25.12036307336718</v>
+        <v>25.36319779974436</v>
       </c>
       <c r="H14" t="n">
-        <v>36.50016839942936</v>
+        <v>36.5567773997308</v>
       </c>
       <c r="I14" t="n">
-        <v>3.153202242901008</v>
+        <v>3.011860377488603</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721683271368815</v>
+        <v>4.721708889750039</v>
       </c>
       <c r="K14" t="n">
-        <v>16.27571778279194</v>
+        <v>15.98867438902426</v>
       </c>
       <c r="L14" t="n">
-        <v>44.31941570166412</v>
+        <v>44.237481922035</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89502504322486</v>
+        <v>99.89972448548613</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.85065438762994</v>
+        <v>83.40253404209524</v>
       </c>
       <c r="C15" t="n">
-        <v>38.91354522988924</v>
+        <v>39.51991153120721</v>
       </c>
       <c r="D15" t="n">
-        <v>1.479904610165956</v>
+        <v>1.500264126575511</v>
       </c>
       <c r="E15" t="n">
-        <v>12.140845186343</v>
+        <v>12.3212011434498</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562688438977027</v>
+        <v>0.7562320141654699</v>
       </c>
       <c r="G15" t="n">
-        <v>24.57770917009221</v>
+        <v>24.98189728569511</v>
       </c>
       <c r="H15" t="n">
-        <v>36.53879688003924</v>
+        <v>36.604085492022</v>
       </c>
       <c r="I15" t="n">
-        <v>2.630449422731187</v>
+        <v>2.512403891653166</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72668027436064</v>
+        <v>4.726450088534187</v>
       </c>
       <c r="K15" t="n">
-        <v>17.14934561237005</v>
+        <v>16.59746595790475</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84952020654902</v>
+        <v>43.79895972262448</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91241104880831</v>
+        <v>99.91633721173645</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.21006722247139</v>
+        <v>81.08418592590164</v>
       </c>
       <c r="C16" t="n">
-        <v>36.67948084294186</v>
+        <v>37.59019143864409</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3788576877529</v>
+        <v>1.411844424300484</v>
       </c>
       <c r="E16" t="n">
-        <v>11.67754949931153</v>
+        <v>11.94428329823134</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569584015594234</v>
+        <v>0.7568834622507643</v>
       </c>
       <c r="G16" t="n">
-        <v>22.89955920384373</v>
+        <v>23.50956192744825</v>
       </c>
       <c r="H16" t="n">
-        <v>36.57211255546603</v>
+        <v>36.63561769505105</v>
       </c>
       <c r="I16" t="n">
-        <v>2.19403986479139</v>
+        <v>2.095473479552464</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730990009746395</v>
+        <v>4.730521639067277</v>
       </c>
       <c r="K16" t="n">
-        <v>19.78993277752861</v>
+        <v>18.91581407409837</v>
       </c>
       <c r="L16" t="n">
-        <v>43.4575183400092</v>
+        <v>43.42420549026716</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92693196047966</v>
+        <v>99.93021100300963</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.73913927183582</v>
+        <v>82.87429487234823</v>
       </c>
       <c r="C17" t="n">
-        <v>37.78373891939821</v>
+        <v>38.88187285878482</v>
       </c>
       <c r="D17" t="n">
-        <v>1.380111803987958</v>
+        <v>1.413038928340339</v>
       </c>
       <c r="E17" t="n">
-        <v>12.40992570869881</v>
+        <v>12.75986287418302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576468800217702</v>
+        <v>0.7575238305079156</v>
       </c>
       <c r="G17" t="n">
-        <v>23.27042007494087</v>
+        <v>23.9843435940839</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9554090617163</v>
+        <v>37.12150478263244</v>
       </c>
       <c r="I17" t="n">
-        <v>2.230332742334039</v>
+        <v>2.103496921926134</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735293000136062</v>
+        <v>4.734523940674473</v>
       </c>
       <c r="K17" t="n">
-        <v>18.2608607281642</v>
+        <v>17.12570512765179</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88112348493725</v>
+        <v>43.9223647221189</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92572313249966</v>
+        <v>99.9299427085555</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.26016741375032</v>
+        <v>80.6735208612152</v>
       </c>
       <c r="C18" t="n">
-        <v>35.64890104599924</v>
+        <v>37.00614756624967</v>
       </c>
       <c r="D18" t="n">
-        <v>1.288803598447936</v>
+        <v>1.332504986605685</v>
       </c>
       <c r="E18" t="n">
-        <v>11.89889570284126</v>
+        <v>12.32499856874926</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582395577561568</v>
+        <v>0.7580728899120363</v>
       </c>
       <c r="G18" t="n">
-        <v>21.7308489379753</v>
+        <v>22.61739347628456</v>
       </c>
       <c r="H18" t="n">
-        <v>36.98431784322596</v>
+        <v>37.14841074977851</v>
       </c>
       <c r="I18" t="n">
-        <v>1.860064537527744</v>
+        <v>1.754184627934899</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738997235975979</v>
+        <v>4.737955561950227</v>
       </c>
       <c r="K18" t="n">
-        <v>20.73983258624965</v>
+        <v>19.32647913878482</v>
       </c>
       <c r="L18" t="n">
-        <v>43.54931268046406</v>
+        <v>43.60894282491203</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93804631271294</v>
+        <v>99.94156952994651</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.19092635410105</v>
+        <v>79.87220856753187</v>
       </c>
       <c r="C19" t="n">
-        <v>34.86588903425022</v>
+        <v>36.4752943817481</v>
       </c>
       <c r="D19" t="n">
-        <v>1.250165243817161</v>
+        <v>1.303865402600546</v>
       </c>
       <c r="E19" t="n">
-        <v>11.80067972164035</v>
+        <v>12.30388235121397</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587409327479671</v>
+        <v>0.7585356470238213</v>
       </c>
       <c r="G19" t="n">
-        <v>21.0793577032329</v>
+        <v>22.13127691615718</v>
       </c>
       <c r="H19" t="n">
-        <v>37.00877319096676</v>
+        <v>37.17108758137971</v>
       </c>
       <c r="I19" t="n">
-        <v>1.551078732021127</v>
+        <v>1.462712875257768</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742130829674792</v>
+        <v>4.740847793898883</v>
       </c>
       <c r="K19" t="n">
-        <v>21.80907364589894</v>
+        <v>20.12779143246811</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27336886047506</v>
+        <v>43.34818683500782</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94833154062422</v>
+        <v>99.95127264922402</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.51227683044885</v>
+        <v>77.4850006673624</v>
       </c>
       <c r="C20" t="n">
-        <v>32.42572167945577</v>
+        <v>34.31350698283404</v>
       </c>
       <c r="D20" t="n">
-        <v>1.152705908383404</v>
+        <v>1.217411368216231</v>
       </c>
       <c r="E20" t="n">
-        <v>11.09628280122204</v>
+        <v>11.69132289173825</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591740995451541</v>
+        <v>0.7589336100537019</v>
       </c>
       <c r="G20" t="n">
-        <v>19.43607078313357</v>
+        <v>20.66384157224659</v>
       </c>
       <c r="H20" t="n">
-        <v>37.02990157755966</v>
+        <v>37.19058926029999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.293303538447825</v>
+        <v>1.219566901972007</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744838122157212</v>
+        <v>4.743335062835636</v>
       </c>
       <c r="K20" t="n">
-        <v>24.48772316955115</v>
+        <v>22.51499933263761</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04346963065915</v>
+        <v>43.13086277132673</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95691447966607</v>
+        <v>99.95936908679838</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.49299548742704</v>
+        <v>83.15859919002105</v>
       </c>
       <c r="C21" t="n">
-        <v>36.06770949343159</v>
+        <v>37.7950917053025</v>
       </c>
       <c r="D21" t="n">
-        <v>1.153619251202875</v>
+        <v>1.21828410050079</v>
       </c>
       <c r="E21" t="n">
-        <v>13.07967516277106</v>
+        <v>13.5817726128234</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597756287014681</v>
+        <v>0.7594776709033236</v>
       </c>
       <c r="G21" t="n">
-        <v>21.10321758438161</v>
+        <v>22.26265169327345</v>
       </c>
       <c r="H21" t="n">
-        <v>38.71098879405691</v>
+        <v>38.80124700049873</v>
       </c>
       <c r="I21" t="n">
-        <v>1.937121386928943</v>
+        <v>1.788430668875588</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748597679384174</v>
+        <v>4.746735443145773</v>
       </c>
       <c r="K21" t="n">
-        <v>18.50700451257297</v>
+        <v>16.84140080997895</v>
       </c>
       <c r="L21" t="n">
-        <v>45.36076640298826</v>
+        <v>45.30393583454104</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93548040899282</v>
+        <v>99.9404283498225</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_25_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.90800215786603</v>
+        <v>45.95992135153207</v>
       </c>
       <c r="M2" t="n">
-        <v>101.4339754146248</v>
+        <v>99.15226822306468</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05073790880499</v>
+        <v>88.08749454285203</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93393658262108</v>
+        <v>45.97065517394454</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228786718756852</v>
+        <v>2.228853095790583</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710647605850639</v>
+        <v>5.73355300746708</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429289062522839</v>
+        <v>0.7429510319301944</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97469835062579</v>
+        <v>33.98707498979868</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17472968760506</v>
+        <v>34.17574746878894</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575640975637596</v>
+        <v>6.575870999512824</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643305664076775</v>
+        <v>4.643443949563714</v>
       </c>
       <c r="K3" t="n">
-        <v>11.949262091195</v>
+        <v>11.912505457148</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88077547695217</v>
+        <v>48.88081229249109</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639741507683</v>
+        <v>106.7639729235836</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.2111975179071</v>
+        <v>87.22336047070701</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73080465942621</v>
+        <v>42.74161346944055</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188728215682761</v>
+        <v>2.187521167847465</v>
       </c>
       <c r="E4" t="n">
-        <v>6.523209086363865</v>
+        <v>6.542461899477436</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444881756188095</v>
+        <v>0.7445101844912543</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36406317998955</v>
+        <v>33.35681751023274</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24645607846524</v>
+        <v>34.2474684865977</v>
       </c>
       <c r="I4" t="n">
-        <v>5.491201684169305</v>
+        <v>5.491392568990085</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65305109761756</v>
+        <v>4.653188653070339</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7888024820929</v>
+        <v>12.77663952929299</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29773616471316</v>
+        <v>44.29908391794667</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81734330623229</v>
+        <v>99.8173369166802</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.17872673432306</v>
+        <v>86.17126920142155</v>
       </c>
       <c r="C5" t="n">
-        <v>42.55068477464999</v>
+        <v>42.54191290512317</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138806302127441</v>
+        <v>2.136619433154294</v>
       </c>
       <c r="E5" t="n">
-        <v>7.138442748028337</v>
+        <v>7.154270353796486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458082305166921</v>
+        <v>0.7458304388352104</v>
       </c>
       <c r="G5" t="n">
-        <v>32.60307427968147</v>
+        <v>32.58063307825069</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30717860376784</v>
+        <v>34.30820018641968</v>
       </c>
       <c r="I5" t="n">
-        <v>4.584115129471955</v>
+        <v>4.584275468245122</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661301440729326</v>
+        <v>4.661440242720065</v>
       </c>
       <c r="K5" t="n">
-        <v>13.82127326567696</v>
+        <v>13.82873079857845</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47550857955721</v>
+        <v>43.47681761382644</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84746661988416</v>
+        <v>99.84746131752806</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.87648468677946</v>
+        <v>84.93543219120583</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96057216968146</v>
+        <v>42.01822121996609</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075415134803628</v>
+        <v>2.076670647041345</v>
       </c>
       <c r="E6" t="n">
-        <v>7.564508769111014</v>
+        <v>7.591198400825354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469288156223994</v>
+        <v>0.7469503176291385</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63676567339101</v>
+        <v>31.6664930243296</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35872551863037</v>
+        <v>34.35971461094037</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825835677581034</v>
+        <v>3.825965705257904</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668305097639997</v>
+        <v>4.668439485182116</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12351531322054</v>
+        <v>15.06456780879418</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78857598572379</v>
+        <v>42.78986998601067</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87266346862579</v>
+        <v>99.87265901477095</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.46247062248813</v>
+        <v>83.47013499745542</v>
       </c>
       <c r="C7" t="n">
-        <v>41.14097039496741</v>
+        <v>41.14739932180531</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006873075770615</v>
+        <v>2.005606573064812</v>
       </c>
       <c r="E7" t="n">
-        <v>7.846729014009187</v>
+        <v>7.863487676551577</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478810966498984</v>
+        <v>0.7479025709201915</v>
       </c>
       <c r="G7" t="n">
-        <v>30.59193901484188</v>
+        <v>30.58285946593919</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40253044589533</v>
+        <v>34.4035182623288</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192261121259346</v>
+        <v>3.192369380399655</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674256854061865</v>
+        <v>4.674391068251197</v>
       </c>
       <c r="K7" t="n">
-        <v>16.53752937751188</v>
+        <v>16.52986500254458</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21522701425456</v>
+        <v>42.21645885050407</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89372678673385</v>
+        <v>99.89372317485396</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.28355762169917</v>
+        <v>88.45898490974038</v>
       </c>
       <c r="C8" t="n">
-        <v>43.42873516199653</v>
+        <v>43.5370628964288</v>
       </c>
       <c r="D8" t="n">
-        <v>2.011119041048955</v>
+        <v>2.009889885649704</v>
       </c>
       <c r="E8" t="n">
-        <v>9.667996216005543</v>
+        <v>9.756612138870221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494633975970988</v>
+        <v>0.7494998435544752</v>
       </c>
       <c r="G8" t="n">
-        <v>31.09203919978141</v>
+        <v>31.11404180131256</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47531628946655</v>
+        <v>34.47699280350585</v>
       </c>
       <c r="I8" t="n">
-        <v>5.603477242817765</v>
+        <v>5.667574414632103</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684146234981868</v>
+        <v>4.68437402221547</v>
       </c>
       <c r="K8" t="n">
-        <v>11.7164423783008</v>
+        <v>11.54101509025963</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66843422874314</v>
+        <v>44.73340547515893</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81361176904048</v>
+        <v>99.81148346184736</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.3102903205577</v>
+        <v>86.4614001856992</v>
       </c>
       <c r="C9" t="n">
-        <v>42.32561128146065</v>
+        <v>42.41962205848916</v>
       </c>
       <c r="D9" t="n">
-        <v>1.921800898919705</v>
+        <v>1.91975499106323</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01828639473393</v>
+        <v>10.10766918367954</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508174232001448</v>
+        <v>0.7508670544644986</v>
       </c>
       <c r="G9" t="n">
-        <v>29.71117455693767</v>
+        <v>29.71871119243499</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53760146720666</v>
+        <v>34.53988450536693</v>
       </c>
       <c r="I9" t="n">
-        <v>4.678000684558683</v>
+        <v>4.731594168286904</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692608895000905</v>
+        <v>4.692919090403116</v>
       </c>
       <c r="K9" t="n">
-        <v>13.68970967944229</v>
+        <v>13.53859981430078</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82902689346322</v>
+        <v>43.88434550458141</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84434785436616</v>
+        <v>99.84256737737135</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.11011121805556</v>
+        <v>84.15963062634317</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85162248858913</v>
+        <v>40.85239871899272</v>
       </c>
       <c r="D10" t="n">
-        <v>1.823100586058678</v>
+        <v>1.816742096553633</v>
       </c>
       <c r="E10" t="n">
-        <v>10.15449247988671</v>
+        <v>10.22349152021403</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519791804457482</v>
+        <v>0.7520415273344758</v>
       </c>
       <c r="G10" t="n">
-        <v>28.18526090694054</v>
+        <v>28.12402308104638</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59104230050442</v>
+        <v>34.59391025738588</v>
       </c>
       <c r="I10" t="n">
-        <v>3.904365886433531</v>
+        <v>3.949162597968292</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699869877785926</v>
+        <v>4.700259545840473</v>
       </c>
       <c r="K10" t="n">
-        <v>15.88988878194443</v>
+        <v>15.84036937365684</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12854426600647</v>
+        <v>43.17579873600913</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87005553654004</v>
+        <v>99.86856682865869</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.8445580371171</v>
+        <v>81.69283733782478</v>
       </c>
       <c r="C11" t="n">
-        <v>39.19155301217567</v>
+        <v>38.99799974190352</v>
       </c>
       <c r="D11" t="n">
-        <v>1.722543591335215</v>
+        <v>1.707454918772416</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1373924004183</v>
+        <v>10.1577237665583</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529769721655033</v>
+        <v>0.7530527433266526</v>
       </c>
       <c r="G11" t="n">
-        <v>26.6306428271856</v>
+        <v>26.43220611032059</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63694071961316</v>
+        <v>34.64042619302601</v>
       </c>
       <c r="I11" t="n">
-        <v>3.257955450364916</v>
+        <v>3.295393960029237</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706106076034396</v>
+        <v>4.706579645791578</v>
       </c>
       <c r="K11" t="n">
-        <v>18.15544196288288</v>
+        <v>18.30716266217521</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54455041698496</v>
+        <v>42.5851386348666</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89154539204353</v>
+        <v>99.89030103894532</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.57434487996272</v>
+        <v>79.17256671215543</v>
       </c>
       <c r="C12" t="n">
-        <v>37.42583644650092</v>
+        <v>36.98786051886824</v>
       </c>
       <c r="D12" t="n">
-        <v>1.622791810983053</v>
+        <v>1.596937255976287</v>
       </c>
       <c r="E12" t="n">
-        <v>10.00334925126008</v>
+        <v>9.95847277136223</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538342971127501</v>
+        <v>0.7539244250283845</v>
       </c>
       <c r="G12" t="n">
-        <v>25.08847341719397</v>
+        <v>24.72134065218106</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67637766718651</v>
+        <v>34.68052355130568</v>
       </c>
       <c r="I12" t="n">
-        <v>2.718054079271667</v>
+        <v>2.749340399874398</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711464356954688</v>
+        <v>4.712027656427402</v>
       </c>
       <c r="K12" t="n">
-        <v>20.42565512003727</v>
+        <v>20.82743328784456</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05800967095165</v>
+        <v>42.09316747217528</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90950123748985</v>
+        <v>99.90846127888808</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.2601312112333</v>
+        <v>76.53459129408381</v>
       </c>
       <c r="C13" t="n">
-        <v>35.53174261883036</v>
+        <v>34.77455251979221</v>
       </c>
       <c r="D13" t="n">
-        <v>1.521990544350319</v>
+        <v>1.482290168813352</v>
       </c>
       <c r="E13" t="n">
-        <v>9.75985842397511</v>
+        <v>9.625769791273617</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545716929136753</v>
+        <v>0.7546774851311812</v>
       </c>
       <c r="G13" t="n">
-        <v>23.5300788768599</v>
+        <v>22.94654976047348</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71029787402907</v>
+        <v>34.71516431603432</v>
       </c>
       <c r="I13" t="n">
-        <v>2.267260718394747</v>
+        <v>2.29340549028798</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716073080710471</v>
+        <v>4.716734282069881</v>
       </c>
       <c r="K13" t="n">
-        <v>22.73986878876671</v>
+        <v>23.4654087059162</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65288709020092</v>
+        <v>41.68366820762841</v>
       </c>
       <c r="M13" t="n">
-        <v>99.924498497798</v>
+        <v>99.9236294333368</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.01132561097575</v>
+        <v>83.54589865934643</v>
       </c>
       <c r="C14" t="n">
-        <v>39.67356817442688</v>
+        <v>39.04260560923364</v>
       </c>
       <c r="D14" t="n">
-        <v>1.523809355874481</v>
+        <v>1.484131878074639</v>
       </c>
       <c r="E14" t="n">
-        <v>12.07849836602747</v>
+        <v>12.01652801025013</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554734223600061</v>
+        <v>0.7556151534385704</v>
       </c>
       <c r="G14" t="n">
-        <v>25.36319779974436</v>
+        <v>24.83484004951919</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5567773997308</v>
+        <v>36.61807682067284</v>
       </c>
       <c r="I14" t="n">
-        <v>3.011860377488603</v>
+        <v>3.114112038399989</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721708889750039</v>
+        <v>4.722594708991064</v>
       </c>
       <c r="K14" t="n">
-        <v>15.98867438902426</v>
+        <v>16.45410134065358</v>
       </c>
       <c r="L14" t="n">
-        <v>44.237481922035</v>
+        <v>44.39961812905181</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89972448548613</v>
+        <v>99.89632507893903</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.40253404209524</v>
+        <v>82.63214680109574</v>
       </c>
       <c r="C15" t="n">
-        <v>39.51991153120721</v>
+        <v>38.58957297890458</v>
       </c>
       <c r="D15" t="n">
-        <v>1.500264126575511</v>
+        <v>1.447913985126354</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3212011434498</v>
+        <v>12.17657954199631</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562320141654699</v>
+        <v>0.7564069948908879</v>
       </c>
       <c r="G15" t="n">
-        <v>24.98189728569511</v>
+        <v>24.24911212167656</v>
       </c>
       <c r="H15" t="n">
-        <v>36.604085492022</v>
+        <v>36.67677756462179</v>
       </c>
       <c r="I15" t="n">
-        <v>2.512403891653166</v>
+        <v>2.597812874715784</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726450088534187</v>
+        <v>4.727543718068048</v>
       </c>
       <c r="K15" t="n">
-        <v>16.59746595790475</v>
+        <v>17.36785319890426</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79895972262448</v>
+        <v>43.95607071001341</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91633721173645</v>
+        <v>99.91349688782223</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.08418592590164</v>
+        <v>79.90063016356983</v>
       </c>
       <c r="C16" t="n">
-        <v>37.59019143864409</v>
+        <v>36.25930334987474</v>
       </c>
       <c r="D16" t="n">
-        <v>1.411844424300484</v>
+        <v>1.344702122877254</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94428329823134</v>
+        <v>11.66972815730402</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568834622507643</v>
+        <v>0.7570907539634413</v>
       </c>
       <c r="G16" t="n">
-        <v>23.50956192744825</v>
+        <v>22.52055915121331</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63561769505105</v>
+        <v>36.70993177866426</v>
       </c>
       <c r="I16" t="n">
-        <v>2.095473479552464</v>
+        <v>2.166800987276055</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730521639067277</v>
+        <v>4.731817212271507</v>
       </c>
       <c r="K16" t="n">
-        <v>18.91581407409837</v>
+        <v>20.09936983643016</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42420549026716</v>
+        <v>43.56916534495299</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93021100300963</v>
+        <v>99.92783853125789</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.87429487234823</v>
+        <v>81.62833922593451</v>
       </c>
       <c r="C17" t="n">
-        <v>38.88187285878482</v>
+        <v>37.49714213499611</v>
       </c>
       <c r="D17" t="n">
-        <v>1.413038928340339</v>
+        <v>1.345909478569243</v>
       </c>
       <c r="E17" t="n">
-        <v>12.75986287418302</v>
+        <v>12.46650518666035</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575238305079156</v>
+        <v>0.7577705162807596</v>
       </c>
       <c r="G17" t="n">
-        <v>23.9843435940839</v>
+        <v>22.96062417778754</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12150478263244</v>
+        <v>37.16273689058234</v>
       </c>
       <c r="I17" t="n">
-        <v>2.103496921926134</v>
+        <v>2.198727249299509</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734523940674473</v>
+        <v>4.736065726754746</v>
       </c>
       <c r="K17" t="n">
-        <v>17.12570512765179</v>
+        <v>18.3716607740655</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9223647221189</v>
+        <v>44.05797192865126</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9299427085555</v>
+        <v>99.92677483771286</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.6735208612152</v>
+        <v>78.98263715523683</v>
       </c>
       <c r="C18" t="n">
-        <v>37.00614756624967</v>
+        <v>35.19048607322514</v>
       </c>
       <c r="D18" t="n">
-        <v>1.332504986605685</v>
+        <v>1.250042246818798</v>
       </c>
       <c r="E18" t="n">
-        <v>12.32499856874926</v>
+        <v>11.88414873569305</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580728899120363</v>
+        <v>0.7583569391421082</v>
       </c>
       <c r="G18" t="n">
-        <v>22.61739347628456</v>
+        <v>21.3251713377297</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14841074977851</v>
+        <v>37.19149636067876</v>
       </c>
       <c r="I18" t="n">
-        <v>1.754184627934899</v>
+        <v>1.833690665536235</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737955561950227</v>
+        <v>4.739730869638175</v>
       </c>
       <c r="K18" t="n">
-        <v>19.32647913878482</v>
+        <v>21.01736284476318</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60894282491203</v>
+        <v>43.73107532508668</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94156952994651</v>
+        <v>99.93892424307499</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.87220856753187</v>
+        <v>77.89601916122237</v>
       </c>
       <c r="C19" t="n">
-        <v>36.4752943817481</v>
+        <v>34.38578052447146</v>
       </c>
       <c r="D19" t="n">
-        <v>1.303865402600546</v>
+        <v>1.211416408112948</v>
       </c>
       <c r="E19" t="n">
-        <v>12.30388235121397</v>
+        <v>11.77177887854975</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585356470238213</v>
+        <v>0.758853149757307</v>
       </c>
       <c r="G19" t="n">
-        <v>22.13127691615718</v>
+        <v>20.66623150544643</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17108758137971</v>
+        <v>37.21583162331929</v>
       </c>
       <c r="I19" t="n">
-        <v>1.462712875257768</v>
+        <v>1.529075410053479</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740847793898883</v>
+        <v>4.742832185983167</v>
       </c>
       <c r="K19" t="n">
-        <v>20.12779143246811</v>
+        <v>22.10398083877764</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34818683500782</v>
+        <v>43.45930278493046</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95127264922402</v>
+        <v>99.94906414817956</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.4850006673624</v>
+        <v>75.10876870652638</v>
       </c>
       <c r="C20" t="n">
-        <v>34.31350698283404</v>
+        <v>31.8334010719001</v>
       </c>
       <c r="D20" t="n">
-        <v>1.217411368216231</v>
+        <v>1.111700994822348</v>
       </c>
       <c r="E20" t="n">
-        <v>11.69132289173825</v>
+        <v>11.01529927521565</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589336100537019</v>
+        <v>0.759282527142461</v>
       </c>
       <c r="G20" t="n">
-        <v>20.66384157224659</v>
+        <v>18.9651303795876</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19058926029999</v>
+        <v>37.23688923700102</v>
       </c>
       <c r="I20" t="n">
-        <v>1.219566901972007</v>
+        <v>1.274950498116913</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743335062835636</v>
+        <v>4.745515794640379</v>
       </c>
       <c r="K20" t="n">
-        <v>22.51499933263761</v>
+        <v>24.89123129347363</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13086277132673</v>
+        <v>43.23289331768036</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95936908679838</v>
+        <v>99.95752568305409</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.15859919002105</v>
+        <v>81.43512146026167</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7950917053025</v>
+        <v>35.72536424410555</v>
       </c>
       <c r="D21" t="n">
-        <v>1.21828410050079</v>
+        <v>1.112559239149615</v>
       </c>
       <c r="E21" t="n">
-        <v>13.5817726128234</v>
+        <v>13.11944592308631</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594776709033236</v>
+        <v>0.7598687008750994</v>
       </c>
       <c r="G21" t="n">
-        <v>22.26265169327345</v>
+        <v>20.76107072080248</v>
       </c>
       <c r="H21" t="n">
-        <v>38.80124700049873</v>
+        <v>39.0469355594659</v>
       </c>
       <c r="I21" t="n">
-        <v>1.788430668875588</v>
+        <v>1.886061936412903</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746735443145773</v>
+        <v>4.74917938046937</v>
       </c>
       <c r="K21" t="n">
-        <v>16.84140080997895</v>
+        <v>18.56487853973831</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30393583454104</v>
+        <v>45.64693698279312</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9404283498225</v>
+        <v>99.93717976663699</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_25_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.95992135153207</v>
+        <v>43.73754898821605</v>
       </c>
       <c r="M2" t="n">
-        <v>99.15226822306468</v>
+        <v>93.61568554468698</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08749454285203</v>
+        <v>81.33369279116145</v>
       </c>
       <c r="C3" t="n">
-        <v>45.97065517394454</v>
+        <v>43.08924834671701</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228853095790583</v>
+        <v>2.172700453332101</v>
       </c>
       <c r="E3" t="n">
-        <v>5.73355300746708</v>
+        <v>4.13334224213021</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429510319301944</v>
+        <v>0.7375317406704578</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98707498979868</v>
+        <v>32.68103598553703</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17574746878894</v>
+        <v>33.92646007084105</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575870999512824</v>
+        <v>3.073048919460241</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643443949563714</v>
+        <v>4.609573379190361</v>
       </c>
       <c r="K3" t="n">
-        <v>11.912505457148</v>
+        <v>18.66630720883855</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88081229249109</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639729235836</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22336047070701</v>
+        <v>88.20510139914646</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74161346944055</v>
+        <v>42.68121605199362</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187521167847465</v>
+        <v>2.178267174151838</v>
       </c>
       <c r="E4" t="n">
-        <v>6.542461899477436</v>
+        <v>6.496706432231371</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445101844912543</v>
+        <v>0.7394213860146701</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35681751023274</v>
+        <v>33.37617548700607</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2474684865977</v>
+        <v>34.01338375667482</v>
       </c>
       <c r="I4" t="n">
-        <v>5.491392568990085</v>
+        <v>6.779763500476003</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653188653070339</v>
+        <v>4.621383662591688</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77663952929299</v>
+        <v>11.79489860085354</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29908391794667</v>
+        <v>45.29847076982634</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8173369166802</v>
+        <v>99.77458542267351</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.17126920142155</v>
+        <v>86.60801633313518</v>
       </c>
       <c r="C5" t="n">
-        <v>42.54191290512317</v>
+        <v>42.13511923290322</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136619433154294</v>
+        <v>2.100104116340682</v>
       </c>
       <c r="E5" t="n">
-        <v>7.154270353796486</v>
+        <v>7.207270068679948</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458304388352104</v>
+        <v>0.7410327414532544</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58063307825069</v>
+        <v>32.17853363431556</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30820018641968</v>
+        <v>34.08750610684969</v>
       </c>
       <c r="I5" t="n">
-        <v>4.584275468245122</v>
+        <v>5.662115031413189</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661440242720065</v>
+        <v>4.631454634082839</v>
       </c>
       <c r="K5" t="n">
-        <v>13.82873079857845</v>
+        <v>13.39198366686483</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47681761382644</v>
+        <v>44.28457033632984</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84746131752806</v>
+        <v>99.8116732360979</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.93543219120583</v>
+        <v>84.71526225368018</v>
       </c>
       <c r="C6" t="n">
-        <v>42.01822121996609</v>
+        <v>41.12059134680851</v>
       </c>
       <c r="D6" t="n">
-        <v>2.076670647041345</v>
+        <v>2.008016965968437</v>
       </c>
       <c r="E6" t="n">
-        <v>7.591198400825354</v>
+        <v>7.679107172175727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469503176291385</v>
+        <v>0.7424110897641507</v>
       </c>
       <c r="G6" t="n">
-        <v>31.6664930243296</v>
+        <v>30.76754193991099</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35971461094037</v>
+        <v>34.15091012915092</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825965705257904</v>
+        <v>4.727205645684028</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668439485182116</v>
+        <v>4.640069311025941</v>
       </c>
       <c r="K6" t="n">
-        <v>15.06456780879418</v>
+        <v>15.28473774631981</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78986998601067</v>
+        <v>43.43738993377686</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87265901477095</v>
+        <v>99.84271902690517</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.47013499745542</v>
+        <v>82.59073560792139</v>
       </c>
       <c r="C7" t="n">
-        <v>41.14739932180531</v>
+        <v>39.72910686173883</v>
       </c>
       <c r="D7" t="n">
-        <v>2.005606573064812</v>
+        <v>1.905593188853362</v>
       </c>
       <c r="E7" t="n">
-        <v>7.863487676551577</v>
+        <v>7.945017543063405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479025709201915</v>
+        <v>0.7435933311186924</v>
       </c>
       <c r="G7" t="n">
-        <v>30.58285946593919</v>
+        <v>29.19816881635657</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4035182623288</v>
+        <v>34.20529323145984</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192369380399655</v>
+        <v>3.945611177577684</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674391068251197</v>
+        <v>4.647458319491827</v>
       </c>
       <c r="K7" t="n">
-        <v>16.52986500254458</v>
+        <v>17.40926439207863</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21645885050407</v>
+        <v>42.73031747824689</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89372317485396</v>
+        <v>99.86868873206434</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.45898490974038</v>
+        <v>80.26255011317458</v>
       </c>
       <c r="C8" t="n">
-        <v>43.5370628964288</v>
+        <v>38.01218893708658</v>
       </c>
       <c r="D8" t="n">
-        <v>2.009889885649704</v>
+        <v>1.794427307400922</v>
       </c>
       <c r="E8" t="n">
-        <v>9.756612138870221</v>
+        <v>8.030282892288433</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494998435544752</v>
+        <v>0.7446101129111059</v>
       </c>
       <c r="G8" t="n">
-        <v>31.11404180131256</v>
+        <v>27.49484609655794</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47699280350585</v>
+        <v>34.25206519391086</v>
       </c>
       <c r="I8" t="n">
-        <v>5.667574414632103</v>
+        <v>3.292505304410903</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68437402221547</v>
+        <v>4.653813205694411</v>
       </c>
       <c r="K8" t="n">
-        <v>11.54101509025963</v>
+        <v>19.73744988682541</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73340547515893</v>
+        <v>42.14076086559974</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81148346184736</v>
+        <v>99.89039968951174</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.4614001856992</v>
+        <v>77.81080699575581</v>
       </c>
       <c r="C9" t="n">
-        <v>42.41962205848916</v>
+        <v>36.06971569513004</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91975499106323</v>
+        <v>1.678513646527376</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10766918367954</v>
+        <v>7.969385539367813</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508670544644986</v>
+        <v>0.7454863542966236</v>
       </c>
       <c r="G9" t="n">
-        <v>29.71871119243499</v>
+        <v>25.71877623122419</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53988450536693</v>
+        <v>34.29237229764468</v>
       </c>
       <c r="I9" t="n">
-        <v>4.731594168286904</v>
+        <v>2.74698321234123</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692919090403116</v>
+        <v>4.659289714353897</v>
       </c>
       <c r="K9" t="n">
-        <v>13.53859981430078</v>
+        <v>22.18919300424418</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88434550458141</v>
+        <v>41.64963281994769</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84256737737135</v>
+        <v>99.90854151932191</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.15963062634317</v>
+        <v>83.96061834205139</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85239871899272</v>
+        <v>40.24486835186062</v>
       </c>
       <c r="D10" t="n">
-        <v>1.816742096553633</v>
+        <v>1.680408141795739</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22349152021403</v>
+        <v>10.28397639741324</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520415273344758</v>
+        <v>0.7463277656094039</v>
       </c>
       <c r="G10" t="n">
-        <v>28.12402308104638</v>
+        <v>27.5795793969365</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59391025738588</v>
+        <v>36.16285226116812</v>
       </c>
       <c r="I10" t="n">
-        <v>3.949162597968292</v>
+        <v>2.842925844069617</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700259545840473</v>
+        <v>4.664548535058775</v>
       </c>
       <c r="K10" t="n">
-        <v>15.84036937365684</v>
+        <v>16.03938165794861</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17579873600913</v>
+        <v>43.62109263271815</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86856682865869</v>
+        <v>99.90534264252737</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.69283733782478</v>
+        <v>83.20830507628706</v>
       </c>
       <c r="C11" t="n">
-        <v>38.99799974190352</v>
+        <v>39.81033058703871</v>
       </c>
       <c r="D11" t="n">
-        <v>1.707454918772416</v>
+        <v>1.639571150996857</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1577237665583</v>
+        <v>10.49656626939265</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530527433266526</v>
+        <v>0.747055863517322</v>
       </c>
       <c r="G11" t="n">
-        <v>26.43220611032059</v>
+        <v>26.96597522361348</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64042619302601</v>
+        <v>36.25476183755124</v>
       </c>
       <c r="I11" t="n">
-        <v>3.295393960029237</v>
+        <v>2.435275584232257</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706579645791578</v>
+        <v>4.669099146983263</v>
       </c>
       <c r="K11" t="n">
-        <v>18.30716266217521</v>
+        <v>16.79169492371294</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5851386348666</v>
+        <v>43.31687775230261</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89030103894532</v>
+        <v>99.91890326305425</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.17256671215543</v>
+        <v>80.80326863780843</v>
       </c>
       <c r="C12" t="n">
-        <v>36.98786051886824</v>
+        <v>37.78236478907394</v>
       </c>
       <c r="D12" t="n">
-        <v>1.596937255976287</v>
+        <v>1.540016033792477</v>
       </c>
       <c r="E12" t="n">
-        <v>9.95847277136223</v>
+        <v>10.19772859807904</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539244250283845</v>
+        <v>0.747681804657504</v>
       </c>
       <c r="G12" t="n">
-        <v>24.72134065218106</v>
+        <v>25.32859533785188</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68052355130568</v>
+        <v>36.28513887904153</v>
       </c>
       <c r="I12" t="n">
-        <v>2.749340399874398</v>
+        <v>2.031096705276615</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712027656427402</v>
+        <v>4.6730112791094</v>
       </c>
       <c r="K12" t="n">
-        <v>20.82743328784456</v>
+        <v>19.19673136219156</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09316747217528</v>
+        <v>42.95325730472806</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90846127888808</v>
+        <v>99.93235345599355</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.53459129408381</v>
+        <v>82.14901893835882</v>
       </c>
       <c r="C13" t="n">
-        <v>34.77455251979221</v>
+        <v>38.87088410205541</v>
       </c>
       <c r="D13" t="n">
-        <v>1.482290168813352</v>
+        <v>1.541195377085685</v>
       </c>
       <c r="E13" t="n">
-        <v>9.625769791273617</v>
+        <v>10.89164801353593</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546774851311812</v>
+        <v>0.7482543789050622</v>
       </c>
       <c r="G13" t="n">
-        <v>22.94654976047348</v>
+        <v>25.71955363070025</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71516431603432</v>
+        <v>36.68448768592255</v>
       </c>
       <c r="I13" t="n">
-        <v>2.29340549028798</v>
+        <v>1.887289984052714</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716734282069881</v>
+        <v>4.676589868156639</v>
       </c>
       <c r="K13" t="n">
-        <v>23.4654087059162</v>
+        <v>17.85098106164116</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68366820762841</v>
+        <v>43.21527330948535</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9236294333368</v>
+        <v>99.93713847318193</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.54589865934643</v>
+        <v>79.77262008041309</v>
       </c>
       <c r="C14" t="n">
-        <v>39.04260560923364</v>
+        <v>36.78637615117739</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484131878074639</v>
+        <v>1.446149296132436</v>
       </c>
       <c r="E14" t="n">
-        <v>12.01652801025013</v>
+        <v>10.48225209229103</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556151534385704</v>
+        <v>0.7487464377548648</v>
       </c>
       <c r="G14" t="n">
-        <v>24.83484004951919</v>
+        <v>24.13341937880063</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61807682067284</v>
+        <v>36.70861173694748</v>
       </c>
       <c r="I14" t="n">
-        <v>3.114112038399989</v>
+        <v>1.57377590251875</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722594708991064</v>
+        <v>4.679665235967906</v>
       </c>
       <c r="K14" t="n">
-        <v>16.45410134065358</v>
+        <v>20.2273799195869</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39961812905181</v>
+        <v>42.93381920745645</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89632507893903</v>
+        <v>99.94757527822074</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.63214680109574</v>
+        <v>78.76141012756185</v>
       </c>
       <c r="C15" t="n">
-        <v>38.58957297890458</v>
+        <v>35.97433782304304</v>
       </c>
       <c r="D15" t="n">
-        <v>1.447913985126354</v>
+        <v>1.40383810005072</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17657954199631</v>
+        <v>10.40733015609</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564069948908879</v>
+        <v>0.7491734363491953</v>
       </c>
       <c r="G15" t="n">
-        <v>24.24911212167656</v>
+        <v>23.43451174292581</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67677756462179</v>
+        <v>36.73673003722397</v>
       </c>
       <c r="I15" t="n">
-        <v>2.597812874715784</v>
+        <v>1.347492677739683</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727543718068048</v>
+        <v>4.682333977182471</v>
       </c>
       <c r="K15" t="n">
-        <v>17.36785319890426</v>
+        <v>21.23858987243816</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95607071001341</v>
+        <v>42.74218148247386</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91349688782223</v>
+        <v>99.95510917795505</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.90063016356983</v>
+        <v>76.1129198933841</v>
       </c>
       <c r="C16" t="n">
-        <v>36.25930334987474</v>
+        <v>33.53351496203516</v>
       </c>
       <c r="D16" t="n">
-        <v>1.344702122877254</v>
+        <v>1.298987341865236</v>
       </c>
       <c r="E16" t="n">
-        <v>11.66972815730402</v>
+        <v>9.81726466527534</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570907539634413</v>
+        <v>0.7495420416085258</v>
       </c>
       <c r="G16" t="n">
-        <v>22.52055915121331</v>
+        <v>21.68421993658174</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70993177866426</v>
+        <v>36.75480509333956</v>
       </c>
       <c r="I16" t="n">
-        <v>2.166800987276055</v>
+        <v>1.123463054660385</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731817212271507</v>
+        <v>4.684637760053286</v>
       </c>
       <c r="K16" t="n">
-        <v>20.09936983643016</v>
+        <v>23.88708010661591</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56916534495299</v>
+        <v>42.54197457918951</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92783853125789</v>
+        <v>99.96256964784058</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.62833922593451</v>
+        <v>82.07033185986347</v>
       </c>
       <c r="C17" t="n">
-        <v>37.49714213499611</v>
+        <v>37.48469625979124</v>
       </c>
       <c r="D17" t="n">
-        <v>1.345909478569243</v>
+        <v>1.29964235792564</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46650518666035</v>
+        <v>11.89400838489653</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577705162807596</v>
+        <v>0.7499199991600569</v>
       </c>
       <c r="G17" t="n">
-        <v>22.96062417778754</v>
+        <v>23.56002722476041</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16273689058234</v>
+        <v>38.63821174372848</v>
       </c>
       <c r="I17" t="n">
-        <v>2.198727249299509</v>
+        <v>1.241522154641992</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736065726754746</v>
+        <v>4.686999994750355</v>
       </c>
       <c r="K17" t="n">
-        <v>18.3716607740655</v>
+        <v>17.92966814013654</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05797192865126</v>
+        <v>44.54427238570557</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92677483771286</v>
+        <v>99.95863678563335</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.98263715523683</v>
+        <v>83.90070227966122</v>
       </c>
       <c r="C18" t="n">
-        <v>35.19048607322514</v>
+        <v>38.24944084459739</v>
       </c>
       <c r="D18" t="n">
-        <v>1.250042246818798</v>
+        <v>1.300805691139777</v>
       </c>
       <c r="E18" t="n">
-        <v>11.88414873569305</v>
+        <v>12.52749696443368</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583569391421082</v>
+        <v>0.7505912660187031</v>
       </c>
       <c r="G18" t="n">
-        <v>21.3251713377297</v>
+        <v>23.70478468440576</v>
       </c>
       <c r="H18" t="n">
-        <v>37.19149636067876</v>
+        <v>38.67279750094254</v>
       </c>
       <c r="I18" t="n">
-        <v>1.833690665536235</v>
+        <v>2.25303076010385</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739730869638175</v>
+        <v>4.691195412616893</v>
       </c>
       <c r="K18" t="n">
-        <v>21.01736284476318</v>
+        <v>16.09929772033879</v>
       </c>
       <c r="L18" t="n">
-        <v>43.73107532508668</v>
+        <v>45.57622757388367</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93892424307499</v>
+        <v>99.92496613881985</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.89601916122237</v>
+        <v>80.83802250653876</v>
       </c>
       <c r="C19" t="n">
-        <v>34.38578052447146</v>
+        <v>35.5339197717788</v>
       </c>
       <c r="D19" t="n">
-        <v>1.211416408112948</v>
+        <v>1.195586259096378</v>
       </c>
       <c r="E19" t="n">
-        <v>11.77177887854975</v>
+        <v>11.82733751338671</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758853149757307</v>
+        <v>0.7511728183533827</v>
       </c>
       <c r="G19" t="n">
-        <v>20.66623150544643</v>
+        <v>21.78735458843286</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21583162331929</v>
+        <v>38.7027608867338</v>
       </c>
       <c r="I19" t="n">
-        <v>1.529075410053479</v>
+        <v>1.878980325827006</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742832185983167</v>
+        <v>4.69483011470864</v>
       </c>
       <c r="K19" t="n">
-        <v>22.10398083877764</v>
+        <v>19.16197749346122</v>
       </c>
       <c r="L19" t="n">
-        <v>43.45930278493046</v>
+        <v>45.24151854697931</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94906414817956</v>
+        <v>99.93741581221934</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.10876870652638</v>
+        <v>77.77898501739909</v>
       </c>
       <c r="C20" t="n">
-        <v>31.8334010719001</v>
+        <v>32.76338317982785</v>
       </c>
       <c r="D20" t="n">
-        <v>1.111700994822348</v>
+        <v>1.091253511997616</v>
       </c>
       <c r="E20" t="n">
-        <v>11.01529927521565</v>
+        <v>11.05637050576678</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759282527142461</v>
+        <v>0.7516772343578452</v>
       </c>
       <c r="G20" t="n">
-        <v>18.9651303795876</v>
+        <v>19.88608269028974</v>
       </c>
       <c r="H20" t="n">
-        <v>37.23688923700102</v>
+        <v>38.72874996878145</v>
       </c>
       <c r="I20" t="n">
-        <v>1.274950498116913</v>
+        <v>1.566868391469141</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745515794640379</v>
+        <v>4.697982714736531</v>
       </c>
       <c r="K20" t="n">
-        <v>24.89123129347363</v>
+        <v>22.2210149826009</v>
       </c>
       <c r="L20" t="n">
-        <v>43.23289331768036</v>
+        <v>44.96340793963161</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95752568305409</v>
+        <v>99.94780610206035</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.43512146026167</v>
+        <v>74.83086538388524</v>
       </c>
       <c r="C21" t="n">
-        <v>35.72536424410555</v>
+        <v>30.05488491882437</v>
       </c>
       <c r="D21" t="n">
-        <v>1.112559239149615</v>
+        <v>0.9914001202306066</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11944592308631</v>
+        <v>10.26242242219252</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598687008750994</v>
+        <v>0.7521146892945993</v>
       </c>
       <c r="G21" t="n">
-        <v>20.76107072080248</v>
+        <v>18.06643878192815</v>
       </c>
       <c r="H21" t="n">
-        <v>39.0469355594659</v>
+        <v>38.75128900827043</v>
       </c>
       <c r="I21" t="n">
-        <v>1.886061936412903</v>
+        <v>1.306483553877682</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74917938046937</v>
+        <v>4.700716808091244</v>
       </c>
       <c r="K21" t="n">
-        <v>18.56487853973831</v>
+        <v>25.16913461611477</v>
       </c>
       <c r="L21" t="n">
-        <v>45.64693698279312</v>
+        <v>44.7324563430756</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93717976663699</v>
+        <v>99.95647587801474</v>
       </c>
     </row>
   </sheetData>
